--- a/out/MLP_Base_repeat_2_000008.xlsx
+++ b/out/MLP_Base_repeat_2_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.247209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.305315212968727</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.305315212968727</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.305315212968727</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-1.305315212968727</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.305315212968727</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001649436542759649</v>
+        <v>-0.0001346919774551643</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.18948857841406</v>
+        <v>-0.1547352121170225</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1548699040944778</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.18979275630597</v>
+        <v>-0.1549868411013528</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5006546092425732</v>
+        <v>0.4204788454175019</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.812477737362266</v>
+        <v>0.6867781845142606</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03567153579313338</v>
+        <v>0.02995902945397344</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3823630947601411</v>
+        <v>0.3255429037842734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06255559141607694</v>
+        <v>0.05253792998839868</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4717910943187426</v>
+        <v>0.4006497362832853</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07599796760034826</v>
+        <v>0.06382706846907771</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5612252292418615</v>
+        <v>0.4757615683698503</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02011080135806813</v>
+        <v>0.01689040652976958</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5253521654565986</v>
+        <v>0.4456331983244352</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01117324035850707</v>
+        <v>0.009382902213194967</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.247209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5275678874362749</v>
+        <v>0.4474932800280596</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02347418172625224</v>
+        <v>0.01971590883467227</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5633594286517477</v>
+        <v>0.4775535218259774</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009219747796403525</v>
+        <v>0.007742237974739839</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5583032693387342</v>
+        <v>0.4733063438525249</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006565277929875261</v>
+        <v>0.005513067497419521</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5622090221668898</v>
+        <v>0.476585801268453</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002580424842602012</v>
+        <v>0.002166268026954105</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.560800839204011</v>
+        <v>0.4754023340202687</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001462425334993015</v>
+        <v>0.001228130533607575</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611439422265685</v>
+        <v>0.4756897031632085</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005539997538044996</v>
+        <v>0.0004647476922726887</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5607879758258527</v>
+        <v>0.4753900822255634</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000257028585533049</v>
+        <v>0.0002151920886832344</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5607475621185706</v>
+        <v>0.4753553845698505</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.107171002812295e-05</v>
+        <v>7.573252943539743e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5606721631606407</v>
+        <v>0.4752914728303587</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.361914509954013e-05</v>
+        <v>1.884928758295011e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5606274301109495</v>
+        <v>0.4752533619556159</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>6.924643791475056e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5606224077716887</v>
+        <v>0.475248343339565</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5606184983953398</v>
+        <v>0.4752442525869778</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5606162474676082</v>
+        <v>0.4752416351835591</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5606106558075999</v>
+        <v>0.4752361179415693</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.560604331813592</v>
+        <v>0.4752297939475614</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5605989640250136</v>
+        <v>0.475224426158983</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5605990007735053</v>
+        <v>0.4752244629074747</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5605991110189809</v>
+        <v>0.4752245731529502</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.305315212968727</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5605991845159645</v>
+        <v>0.4752246466499339</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5605993682584236</v>
+        <v>0.475224830392393</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5606009116950801</v>
+        <v>0.4752263738290495</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-1.305315212968727</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5606023816347532</v>
+        <v>0.4752278437687226</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5606036310834752</v>
+        <v>0.4752290932174446</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5606049907776725</v>
+        <v>0.4752304529116419</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5606027858681633</v>
+        <v>0.4752282480021326</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5606023816347532</v>
+        <v>0.4752278437687226</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5606015364194412</v>
+        <v>0.4752269985534107</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5606020876468185</v>
+        <v>0.4752275497807879</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.560601756910392</v>
+        <v>0.4752272190443615</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5606014629224576</v>
+        <v>0.475226925056427</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5606015364194412</v>
+        <v>0.4752269985534107</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5606010954375392</v>
+        <v>0.4752265575715087</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5606009851920637</v>
+        <v>0.4752264473260331</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.560600948443572</v>
+        <v>0.4752264105775414</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5606010954375392</v>
+        <v>0.4752265575715087</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5606006177071456</v>
+        <v>0.475226079841115</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5606015731679329</v>
+        <v>0.4752270353019024</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5606015364194412</v>
+        <v>0.4752269985534107</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5606012056830149</v>
+        <v>0.4752266678169842</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5606016466649167</v>
+        <v>0.4752271087988862</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5606010219405556</v>
+        <v>0.4752264840745251</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5606008381980965</v>
+        <v>0.4752263003320659</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5606004339646865</v>
+        <v>0.4752258960986559</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5605995887493745</v>
+        <v>0.4752250508833439</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5605995520008829</v>
+        <v>0.4752250141348522</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5605996989948501</v>
+        <v>0.4752251611288195</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5605996254978665</v>
+        <v>0.4752250876318359</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5605996989948501</v>
+        <v>0.4752251611288195</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.560599735743342</v>
+        <v>0.4752251978773114</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.847209366080289</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5605996254978665</v>
+        <v>0.4752250876318359</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5606000664797683</v>
+        <v>0.4752255286137378</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.9209439647931164</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5605999562342928</v>
+        <v>0.4752254183682623</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5605999194858009</v>
+        <v>0.4752253816197703</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5605998459888173</v>
+        <v>0.4752253081227867</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5605998092403256</v>
+        <v>0.475225271374295</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5605995887493745</v>
+        <v>0.4752250508833439</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5605995152523908</v>
+        <v>0.4752249773863603</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5605994417554072</v>
+        <v>0.4752249038893767</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.069469496003421</v>
+        <v>-1.905315212968727</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5605994785038991</v>
+        <v>0.4752249406378686</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.069469496003421</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5605993682584236</v>
+        <v>0.475224830392393</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5605994785038991</v>
+        <v>0.4752249406378686</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.847209366080289</v>
+        <v>1.520943964793116</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5605997724918337</v>
+        <v>0.4752252346258031</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_2_000008.xlsx
+++ b/out/MLP_Base_repeat_2_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.5695108125977835</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.247209366080289</v>
+        <v>0.9485598254073502</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.847209366080289</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-0.367636225830917</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.847209366080289</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-0.367636225830917</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.367636225830917</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001649436542759649</v>
+        <v>-0.0001261981842154637</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.18948857841406</v>
+        <v>-0.1449774750680906</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.847209366080289</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1896535220683359</v>
+        <v>-0.1451036732523061</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.847209366080289</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.18979275630597</v>
+        <v>-0.1452139312148022</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5006546092425732</v>
+        <v>0.396462266174381</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.812477737362266</v>
+        <v>0.6484723376818513</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03567153579313338</v>
+        <v>0.02824788981158971</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.847209366080289</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3823630947601411</v>
+        <v>0.3078693678227595</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06255559141607694</v>
+        <v>0.04953704575737337</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4717910943187426</v>
+        <v>0.3786863994885474</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07599796760034826</v>
+        <v>0.06018166031653096</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5612252292418615</v>
+        <v>0.4495083283729744</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02011080135806813</v>
+        <v>0.01592574019618517</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5253521654565986</v>
+        <v>0.4211006880339377</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01117324035850707</v>
+        <v>0.008846901387313618</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.247209366080289</v>
+        <v>0.9485598254073505</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5275678874362749</v>
+        <v>0.4228542485356161</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02347418172625224</v>
+        <v>0.01858950560230452</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5633594286517477</v>
+        <v>0.4511970978556692</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009219747796403525</v>
+        <v>0.007300196101865048</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5583032693387342</v>
+        <v>0.4471922819210528</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006565277929875261</v>
+        <v>0.0051974043676828</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5622090221668898</v>
+        <v>0.4502838507133126</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002580424842602012</v>
+        <v>0.002042699927859157</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.847209366080289</v>
+        <v>0.1904617997882167</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.560800839204011</v>
+        <v>0.4491677972780373</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001462425334993015</v>
+        <v>0.00115722552792514</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882167</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611439422265685</v>
+        <v>0.449438355195258</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005539997538044996</v>
+        <v>0.0004377371999670092</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5607879758258527</v>
+        <v>0.4491556749615276</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000257028585533049</v>
+        <v>0.0002019805633622404</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5607475621185706</v>
+        <v>0.4491226856681739</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.107171002812295e-05</v>
+        <v>7.088857766927358e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5606721631606407</v>
+        <v>0.4490620146451171</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.361914509954013e-05</v>
+        <v>1.741833032797311e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5606274301109495</v>
+        <v>0.4490255596864324</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>6.447658039816054e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5606224077716887</v>
+        <v>0.4490205418150234</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5606184983953398</v>
+        <v>0.4490164143139445</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5606162474676082</v>
+        <v>0.4490136131680668</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5606106558075999</v>
+        <v>0.4490081694230605</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.560604331813592</v>
+        <v>0.4490021766896302</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5605989640250136</v>
+        <v>0.4489968089010518</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5605990007735053</v>
+        <v>0.4489968456495435</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5605991110189809</v>
+        <v>0.448996955895019</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5605991845159645</v>
+        <v>0.4489970293920026</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5605993682584236</v>
+        <v>0.4489972131344618</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.847209366080289</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5606009116950801</v>
+        <v>0.4489987565711183</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5606023816347532</v>
+        <v>0.4490002265107914</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5606036310834752</v>
+        <v>0.4490014759595133</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5606049907776725</v>
+        <v>0.4490028356537106</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5606027858681633</v>
+        <v>0.4490006307442014</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5606023816347532</v>
+        <v>0.4490002265107914</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.847209366080289</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5606015364194412</v>
+        <v>0.4489993812954794</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5606020876468185</v>
+        <v>0.4489999325228566</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.560601756910392</v>
+        <v>0.4489996017864302</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5606014629224576</v>
+        <v>0.4489993077984957</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5606015364194412</v>
+        <v>0.4489993812954794</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5606010954375392</v>
+        <v>0.4489989403135774</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5606009851920637</v>
+        <v>0.4489988300681019</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.560600948443572</v>
+        <v>0.4489987933196102</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882167</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5606010954375392</v>
+        <v>0.4489989403135774</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5606006177071456</v>
+        <v>0.4489984625831838</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.847209366080289</v>
+        <v>1.14855982540735</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5606015731679329</v>
+        <v>0.4489994180439711</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5606015364194412</v>
+        <v>0.4489993812954794</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-0.367636225830917</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5606012056830149</v>
+        <v>0.448999050559053</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5606016466649167</v>
+        <v>0.4489994915409549</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5606010219405556</v>
+        <v>0.4489988668165938</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5606008381980965</v>
+        <v>0.4489986830741347</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5606004339646865</v>
+        <v>0.4489982788407246</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5605995887493745</v>
+        <v>0.4489974336254126</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5605995520008829</v>
+        <v>0.448997396876921</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5605996989948501</v>
+        <v>0.4489975438708882</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5605996254978665</v>
+        <v>0.4489974703739046</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.847209366080289</v>
+        <v>0.3904617997882168</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5605996989948501</v>
+        <v>0.4489975438708882</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4694694960034206</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.560599735743342</v>
+        <v>0.4489975806193801</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.847209366080289</v>
+        <v>0.3904617997882168</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5605996254978665</v>
+        <v>0.4489974703739046</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4694694960034206</v>
+        <v>0.3904617997882168</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5606000664797683</v>
+        <v>0.4489979113558065</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4694694960034206</v>
+        <v>-0.367636225830917</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5605999562342928</v>
+        <v>0.448997801110331</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5605999194858009</v>
+        <v>0.448997764361839</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5605998459888173</v>
+        <v>0.4489976908648554</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5605998092403256</v>
+        <v>0.4489976541163637</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5605995887493745</v>
+        <v>0.4489974336254126</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5605995152523908</v>
+        <v>0.448997360128429</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5605994417554072</v>
+        <v>0.4489972866314454</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309171</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5605994785038991</v>
+        <v>0.4489973233799373</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5605993682584236</v>
+        <v>0.4489972131344618</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5605994785038991</v>
+        <v>0.4489973233799373</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5605997724918337</v>
+        <v>0.4489976173678718</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_2_000008.xlsx
+++ b/out/MLP_Base_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4556662440299988</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5695108125977835</v>
+        <v>-0.3000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5126062035560608</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9485598254073502</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.590131938457489</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.906657851026484</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5965441465377808</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.906657851026484</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.534494936466217</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.14855982540735</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4794079959392548</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4716530442237854</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.367636225830917</v>
+        <v>0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4300329387187958</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4491308927536011</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4286948442459106</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4525803625583649</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4357606470584869</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4377605617046356</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4289619922637939</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4937089085578918</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4382602870464325</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4067772626876831</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.406785786151886</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4094979465007782</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4055615663528442</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3939051032066345</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4061704874038696</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3977589905261993</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4287314713001251</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4063583314418793</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4018851816654205</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3936719000339508</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4013671875</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4116402268409729</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4337318539619446</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.5685814023017883</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4536822140216827</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4520647823810577</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.367636225830917</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4434153437614441</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.367636225830917</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4159180521965027</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4530920088291168</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4092546999454498</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.406951367855072</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4744162261486053</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.485406905412674</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4806651175022125</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5387116670608521</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.148559825407351</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.5963672399520874</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.906657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5820097923278809</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.148559825407351</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001261981842154637</v>
+        <v>-0.0001228097873588558</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1449774750680906</v>
+        <v>-0.1410848578813508</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.492574155330658</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.14855982540735</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.563313364982605</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4601448476314545</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3904617997882167</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.489950031042099</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4541447758674622</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4526890218257904</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.446165531873703</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4974563121795654</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4678926765918732</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.16</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4852073490619659</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4726530313491821</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4750891923904419</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5074951648712158</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.148559825407351</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1451036732523061</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5642832517623901</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.14855982540735</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1452139312148022</v>
+        <v>-0.1413091442169283</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.396462266174381</v>
+        <v>0.3648865570636502</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4823943972587585</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.14855982540735</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6484723376818513</v>
+        <v>0.5891645654616225</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02824788981158971</v>
+        <v>0.02599805399442605</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5246802568435669</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.14855982540735</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3078693678227595</v>
+        <v>0.2756888716335613</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04953704575737337</v>
+        <v>0.04559172862032112</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5553122162818909</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.148559825407351</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3786863994885474</v>
+        <v>0.3408657824679136</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06018166031653096</v>
+        <v>0.05538887771980253</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4867596924304962</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3904617997882167</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4495083283729744</v>
+        <v>0.4060472145462402</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01592574019618517</v>
+        <v>0.0146571198108624</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4391433298587799</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3904617997882167</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4211006880339377</v>
+        <v>0.3799021898981331</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008846901387313618</v>
+        <v>0.008141772306311598</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6024852395057678</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9485598254073505</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4228542485356161</v>
+        <v>0.3815157028775709</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01858950560230452</v>
+        <v>0.01710869369217399</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.5680286288261414</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.906657851026484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4511970978556692</v>
+        <v>0.4076019796251107</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007300196101865048</v>
+        <v>0.00671888076219409</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5490871667861938</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.148559825407351</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4471922819210528</v>
+        <v>0.4039154514306495</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.0051974043676828</v>
+        <v>0.004783419935241198</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4662597477436066</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.14855982540735</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4502838507133126</v>
+        <v>0.4067606089131804</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002042699927859157</v>
+        <v>0.001879752983997686</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5051709413528442</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1904617997882167</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4491677972780373</v>
+        <v>0.4057329682181124</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.00115722552792514</v>
+        <v>0.001064740737904572</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4475992023944855</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1904617997882167</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.449438355195258</v>
+        <v>0.4059815984496127</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004377371999670092</v>
+        <v>0.0004025061230465574</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.445028156042099</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4491556749615276</v>
+        <v>0.4057210147862057</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002019805633622404</v>
+        <v>0.0001854661567109978</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4155173003673553</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4491226856681739</v>
+        <v>0.4056902528170303</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.088857766927358e-05</v>
+        <v>6.523730060879578e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4408736228942871</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4490620146451171</v>
+        <v>0.4056339996036724</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.741833032797311e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4608222842216492</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4490255596864324</v>
+        <v>0.4056001935149673</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4486961662769318</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4490205418150234</v>
+        <v>0.4055951771328424</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4717997014522552</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4490164143139445</v>
+        <v>0.40559097692352</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4062981903553009</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4490136131680668</v>
+        <v>0.4055879930444143</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.424227774143219</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4490081694230605</v>
+        <v>0.405582549299408</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4410499632358551</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4490021766896302</v>
+        <v>0.4055765565659776</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4590689837932587</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4489968089010518</v>
+        <v>0.4055711887773992</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4693839848041534</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4489968456495435</v>
+        <v>0.4055712255258909</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4649880826473236</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.448996955895019</v>
+        <v>0.4055713357713665</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.440672755241394</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4489970293920026</v>
+        <v>0.4055714092683501</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5059410333633423</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.148559825407351</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4489972131344618</v>
+        <v>0.4055715930108093</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5644001960754395</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.14855982540735</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4489987565711183</v>
+        <v>0.4055731364474657</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3732926249504089</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4490002265107914</v>
+        <v>0.4055746063871388</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3293243646621704</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4490014759595133</v>
+        <v>0.4055758558358608</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8620743751525879</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.148559825407351</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4490028356537106</v>
+        <v>0.4055772155300582</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5661699771881104</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.906657851026484</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4490006307442014</v>
+        <v>0.4055750106205488</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.6263558268547058</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.906657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4490002265107914</v>
+        <v>0.4055746063871388</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5894724130630493</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.14855982540735</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4489993812954794</v>
+        <v>0.4055737611718269</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4912332892417908</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4489999325228566</v>
+        <v>0.4055743123992041</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4598923623561859</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5676362258309171</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4489996017864302</v>
+        <v>0.4055739816627777</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.4888267815113068</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4489993077984957</v>
+        <v>0.4055736876748433</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4559498429298401</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4489993812954794</v>
+        <v>0.4055737611718269</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4395119547843933</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4489989403135774</v>
+        <v>0.4055733201899249</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4288955330848694</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4489988300681019</v>
+        <v>0.4055732099444493</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4482548832893372</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4489987933196102</v>
+        <v>0.4055731731959576</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4316032528877258</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1904617997882167</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4489989403135774</v>
+        <v>0.4055733201899249</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.6173845529556274</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.148559825407351</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4489984625831838</v>
+        <v>0.4055728424595313</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.6434732675552368</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.14855982540735</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4489994180439711</v>
+        <v>0.4055737979203186</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4887003600597382</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4489993812954794</v>
+        <v>0.4055737611718269</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4799426794052124</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.367636225830917</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.448999050559053</v>
+        <v>0.4055734304354005</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4458049237728119</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4489994915409549</v>
+        <v>0.4055738714173024</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4468312561511993</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4489988668165938</v>
+        <v>0.4055732466929413</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4574449956417084</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4489986830741347</v>
+        <v>0.4055730629504821</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4611958265304565</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4489982788407246</v>
+        <v>0.4055726587170721</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4772641062736511</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4489974336254126</v>
+        <v>0.4055718135017601</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4772568941116333</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.448997396876921</v>
+        <v>0.4055717767532684</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4730096757411957</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4489975438708882</v>
+        <v>0.4055719237472357</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4561142027378082</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3904617997882167</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4489974703739046</v>
+        <v>0.4055718502502521</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.5540663599967957</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3904617997882168</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4489975438708882</v>
+        <v>0.4055719237472357</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4502251744270325</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.148559825407351</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4489975806193801</v>
+        <v>0.4055719604957276</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.5238266587257385</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3904617997882168</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4489974703739046</v>
+        <v>0.4055718502502521</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4269837439060211</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3904617997882168</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4489979113558065</v>
+        <v>0.405572291232154</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4495079815387726</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.367636225830917</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.448997801110331</v>
+        <v>0.4055721809866785</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4076807498931885</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.448997764361839</v>
+        <v>0.4055721442381865</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4277764856815338</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4489976908648554</v>
+        <v>0.4055720707412029</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.4166346192359924</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4489976541163637</v>
+        <v>0.4055720339927112</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4061435759067535</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4489974336254126</v>
+        <v>0.4055718135017601</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4504847824573517</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.448997360128429</v>
+        <v>0.4055717400047765</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4290640950202942</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4489972866314454</v>
+        <v>0.4055716665077929</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4203974008560181</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5676362258309171</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4489973233799373</v>
+        <v>0.4055717032562848</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4603976011276245</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4489972131344618</v>
+        <v>0.4055715930108093</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.5177581906318665</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.148559825407351</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4489973233799373</v>
+        <v>0.4055717032562848</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5032569169998169</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.906657851026484</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4489976173678718</v>
+        <v>0.4055719972442193</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_2_000008.xlsx
+++ b/out/MLP_Base_repeat_2_000008.xlsx
@@ -72494,7 +72494,7 @@
         <v>0.6263558268547058</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0.4055746063871388</v>
@@ -73289,7 +73289,7 @@
         <v>0.5894724130630493</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0.4055737611718269</v>
@@ -74084,7 +74084,7 @@
         <v>0.4912332892417908</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0.4055743123992041</v>
@@ -74879,7 +74879,7 @@
         <v>0.4598923623561859</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0.4055739816627777</v>
@@ -75674,7 +75674,7 @@
         <v>0.4888267815113068</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0.4055736876748433</v>
@@ -76469,7 +76469,7 @@
         <v>0.4559498429298401</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0.4055737611718269</v>
@@ -77264,7 +77264,7 @@
         <v>0.4395119547843933</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0.4055733201899249</v>
@@ -80444,7 +80444,7 @@
         <v>0.6173845529556274</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
         <v>0.4055728424595313</v>
@@ -81239,7 +81239,7 @@
         <v>0.6434732675552368</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
         <v>0.4055737979203186</v>
@@ -82034,7 +82034,7 @@
         <v>0.4887003600597382</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0.4055737611718269</v>
@@ -82829,7 +82829,7 @@
         <v>0.4799426794052124</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
         <v>0.4055734304354005</v>
@@ -83624,7 +83624,7 @@
         <v>0.4458049237728119</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0.4055738714173024</v>
@@ -89189,7 +89189,7 @@
         <v>0.4561142027378082</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0.4055718502502521</v>
